--- a/Result/profitability/2887.xlsx
+++ b/Result/profitability/2887.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM97"/>
+  <dimension ref="A1:AM98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,7 +663,7 @@
         <v>0.52</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4475</v>
+        <v>0.50125</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
@@ -766,11 +766,11 @@
         <v>0.41</v>
       </c>
       <c r="M3" t="n">
-        <v>0.45</v>
+        <v>0.49875</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -877,7 +877,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4662500000000001</v>
+        <v>0.54125</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
@@ -988,11 +988,11 @@
         <v>0.48</v>
       </c>
       <c r="M5" t="n">
-        <v>0.49875</v>
+        <v>0.5599999999999999</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -1099,11 +1099,11 @@
         <v>0.47</v>
       </c>
       <c r="M6" t="n">
-        <v>0.51625</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
         <v>0.66</v>
       </c>
       <c r="M7" t="n">
-        <v>0.55</v>
+        <v>0.5862499999999999</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
@@ -1337,7 +1337,7 @@
         <v>0.57</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5549999999999999</v>
+        <v>0.56125</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
@@ -11165,6 +11165,113 @@
         <v>114.4</v>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2887</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>115.1Q</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>47867</v>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="n">
+        <v>25589</v>
+      </c>
+      <c r="K98" t="n">
+        <v>21041</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="n">
+        <v>1</v>
+      </c>
+      <c r="P98" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>1</v>
+      </c>
+      <c r="R98" t="n">
+        <v>0</v>
+      </c>
+      <c r="S98" t="n">
+        <v>0</v>
+      </c>
+      <c r="T98" t="n">
+        <v>0</v>
+      </c>
+      <c r="U98" t="n">
+        <v>1</v>
+      </c>
+      <c r="V98" t="n">
+        <v>115.1</v>
+      </c>
+      <c r="W98" t="n">
+        <v>0.04999999999999993</v>
+      </c>
+      <c r="X98" t="n">
+        <v>0.06493506493506485</v>
+      </c>
+      <c r="Y98" t="inlineStr"/>
+      <c r="Z98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA98" t="n">
+        <v>0.4899999999999999</v>
+      </c>
+      <c r="AB98" t="n">
+        <v>1.484848484848484</v>
+      </c>
+      <c r="AC98" t="inlineStr"/>
+      <c r="AD98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK98" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM98" t="n">
+        <v>115.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
